--- a/src/main/resources/data/customer_data.xlsx
+++ b/src/main/resources/data/customer_data.xlsx
@@ -7,9 +7,9 @@
     <workbookView windowWidth="23040" windowHeight="9324"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="2" sheetId="2" r:id="rId2"/>
+    <sheet name="3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
   <si>
     <t>customer_id</t>
   </si>
@@ -64,19 +64,40 @@
     <t>唐山星梦缘娱乐股份有限公司</t>
   </si>
   <si>
+    <t>363924F1A2AD44E28831A615F70EE381</t>
+  </si>
+  <si>
+    <t>中国石油天然气股份有限公司河北保定销售分公司第三十四加油站</t>
+  </si>
+  <si>
+    <t>2be9a6d1ec8f4593ac7d675b541566e9</t>
+  </si>
+  <si>
     <t>F34CF8F4C2BA4827A1550D5A0DF1CCE4</t>
   </si>
   <si>
     <t>河北BIG大食袋食品公司</t>
   </si>
   <si>
-    <t>363924F1A2AD44E28831A615F70EE381</t>
-  </si>
-  <si>
-    <t>中国石油天然气股份有限公司河北保定销售分公司第三十四加油站</t>
-  </si>
-  <si>
-    <t>2be9a6d1ec8f4593ac7d675b541566e9</t>
+    <t>d9f2860a636944b792d486f6623e4eed</t>
+  </si>
+  <si>
+    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE5</t>
+  </si>
+  <si>
+    <t>684BF6BD5829D2613460D115B0C8B4AD</t>
+  </si>
+  <si>
+    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE6</t>
+  </si>
+  <si>
+    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE7</t>
+  </si>
+  <si>
+    <t>8c9d06c140244485b64a837510f244e2</t>
+  </si>
+  <si>
+    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE8</t>
   </si>
   <si>
     <t>5BBDC0408063411D86F9A7BF3BD6DAB9</t>
@@ -91,88 +112,88 @@
     <t>河北倍智合成材料有限公司</t>
   </si>
   <si>
+    <t>DD330540FE724E0EA8FC0FABD370005E</t>
+  </si>
+  <si>
+    <t>返利协议_客户_03</t>
+  </si>
+  <si>
+    <t>57266D99C9FB72AD09BFBFF4B8AC0218</t>
+  </si>
+  <si>
+    <t>E5289D5821E14398BCDE080569A4674B</t>
+  </si>
+  <si>
+    <t>商务自动化测试代账客户_1761165296003</t>
+  </si>
+  <si>
+    <t>FDF34D4084D24180B386584E55780269</t>
+  </si>
+  <si>
+    <t>河北永洋特钢集团有限公司</t>
+  </si>
+  <si>
+    <t>b763cad2fe2542018602d41fccc4ee39</t>
+  </si>
+  <si>
+    <t>A2E0FB4001604FB5BEE3D0CDBFB335D9</t>
+  </si>
+  <si>
+    <t>河北亿多宸建筑工程有限公司</t>
+  </si>
+  <si>
+    <t>DF910C299FBE1BDD4AC92093ECC77B2A</t>
+  </si>
+  <si>
+    <t>2DA38A922F3948D3AB3718608DC592E1</t>
+  </si>
+  <si>
+    <t>顺昂企业管理有限公司河北分公司</t>
+  </si>
+  <si>
+    <t>A8A6BFE023CF4316B3B3D1D2B79A93D7</t>
+  </si>
+  <si>
+    <t>河北博雅机械制造有限公司沧州分公司</t>
+  </si>
+  <si>
+    <t>4E281275027F40868862718062B99CAA</t>
+  </si>
+  <si>
+    <t>贾会计</t>
+  </si>
+  <si>
+    <t>8A906D0E26EC44C68BB439BDB1A64E8C</t>
+  </si>
+  <si>
+    <t>河北会计客户转联系人</t>
+  </si>
+  <si>
+    <t>5BB9D3A409424BE3AC59180A46DDBC30</t>
+  </si>
+  <si>
+    <t>河北会计客户00</t>
+  </si>
+  <si>
+    <t>9D83346BDBA24B75ADA707AD1BDDF444</t>
+  </si>
+  <si>
+    <t>商务自动化测试代账客户_1761165214745</t>
+  </si>
+  <si>
+    <t>c28cf28dbbd24eb4b4132e11bbfe8697</t>
+  </si>
+  <si>
+    <t>AACEEDA4A2B540DEAB2300BEE464289F</t>
+  </si>
+  <si>
+    <t>个代主联系人回测</t>
+  </si>
+  <si>
     <t>2395C37CB3A04E42BAA3EE0BA3EB74A9</t>
   </si>
   <si>
     <t>ST202508141114test</t>
-  </si>
-  <si>
-    <t>57266D99C9FB72AD09BFBFF4B8AC0218</t>
-  </si>
-  <si>
-    <t>DD330540FE724E0EA8FC0FABD370005E</t>
-  </si>
-  <si>
-    <t>返利协议_客户_03</t>
-  </si>
-  <si>
-    <t>E5289D5821E14398BCDE080569A4674B</t>
-  </si>
-  <si>
-    <t>商务自动化测试代账客户_1761165296003</t>
-  </si>
-  <si>
-    <t>FDF34D4084D24180B386584E55780269</t>
-  </si>
-  <si>
-    <t>河北永洋特钢集团有限公司</t>
-  </si>
-  <si>
-    <t>b763cad2fe2542018602d41fccc4ee39</t>
-  </si>
-  <si>
-    <t>A2E0FB4001604FB5BEE3D0CDBFB335D9</t>
-  </si>
-  <si>
-    <t>河北亿多宸建筑工程有限公司</t>
-  </si>
-  <si>
-    <t>DF910C299FBE1BDD4AC92093ECC77B2A</t>
-  </si>
-  <si>
-    <t>2DA38A922F3948D3AB3718608DC592E1</t>
-  </si>
-  <si>
-    <t>顺昂企业管理有限公司河北分公司</t>
-  </si>
-  <si>
-    <t>A8A6BFE023CF4316B3B3D1D2B79A93D7</t>
-  </si>
-  <si>
-    <t>河北博雅机械制造有限公司沧州分公司</t>
-  </si>
-  <si>
-    <t>4E281275027F40868862718062B99CAA</t>
-  </si>
-  <si>
-    <t>贾会计</t>
-  </si>
-  <si>
-    <t>8A906D0E26EC44C68BB439BDB1A64E8C</t>
-  </si>
-  <si>
-    <t>河北会计客户转联系人</t>
-  </si>
-  <si>
-    <t>5BB9D3A409424BE3AC59180A46DDBC30</t>
-  </si>
-  <si>
-    <t>河北会计客户00</t>
-  </si>
-  <si>
-    <t>9D83346BDBA24B75ADA707AD1BDDF444</t>
-  </si>
-  <si>
-    <t>商务自动化测试代账客户_1761165214745</t>
-  </si>
-  <si>
-    <t>c28cf28dbbd24eb4b4132e11bbfe8697</t>
-  </si>
-  <si>
-    <t>AACEEDA4A2B540DEAB2300BEE464289F</t>
-  </si>
-  <si>
-    <t>个代主联系人回测</t>
   </si>
 </sst>
 </file>
@@ -788,10 +809,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1103,7 +1125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.2222222222222" customWidth="1"/>
@@ -1178,203 +1200,78 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
         <v>17</v>
       </c>
+      <c r="B7">
+        <v>11111</v>
+      </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>11112</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>11113</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>11114</v>
       </c>
       <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1387,9 +1284,130 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="35.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="24.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="14.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="37.1111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1399,9 +1417,113 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="33.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="27.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/src/main/resources/data/customer_data.xlsx
+++ b/src/main/resources/data/customer_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9324"/>
+    <workbookView windowWidth="23040" windowHeight="9324" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
   <si>
     <t>customer_id</t>
   </si>
@@ -40,6 +40,12 @@
     <t>customer_type</t>
   </si>
   <si>
+    <t>servyou_num</t>
+  </si>
+  <si>
+    <t>sale_area_id</t>
+  </si>
+  <si>
     <t>customer_manage_id</t>
   </si>
   <si>
@@ -157,6 +163,33 @@
     <t>河北博雅机械制造有限公司沧州分公司</t>
   </si>
   <si>
+    <t>F12ADE025BFD428880B327BAA6A92993</t>
+  </si>
+  <si>
+    <t>新模型主从客户主机构</t>
+  </si>
+  <si>
+    <t>2NU8S32U</t>
+  </si>
+  <si>
+    <t>23FC022AE7E44237A81E23C07A0A5354</t>
+  </si>
+  <si>
+    <t>河北泊头测试</t>
+  </si>
+  <si>
+    <t>5EM27VZN</t>
+  </si>
+  <si>
+    <t>1600142E993540F2B85F2D212F31AE34</t>
+  </si>
+  <si>
+    <t>唐山3月测试专用机构1</t>
+  </si>
+  <si>
+    <t>AP25PQDU</t>
+  </si>
+  <si>
     <t>4E281275027F40868862718062B99CAA</t>
   </si>
   <si>
@@ -194,6 +227,15 @@
   </si>
   <si>
     <t>ST202508141114test</t>
+  </si>
+  <si>
+    <t>29F27552F248477B9B52C9BCDE62ECAC</t>
+  </si>
+  <si>
+    <t>个人代理合并双写测试02211</t>
+  </si>
+  <si>
+    <t>8M4R7GFW</t>
   </si>
 </sst>
 </file>
@@ -1125,16 +1167,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="33.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="18.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="36.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="14.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="15.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="21.1111111111111" customWidth="1"/>
+    <col min="6" max="6" width="36.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1147,80 +1191,86 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>11111</v>
@@ -1228,13 +1278,15 @@
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>11112</v>
@@ -1242,13 +1294,15 @@
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>11113</v>
@@ -1256,13 +1310,15 @@
       <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>11114</v>
@@ -1270,8 +1326,10 @@
       <c r="C10">
         <v>1</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1284,16 +1342,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="35.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="24.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="37.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="14.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="37.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="17.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="37.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1306,105 +1366,219 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9">
         <v>2</v>
+      </c>
+      <c r="D9">
+        <v>18</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <v>752</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11">
+        <v>752</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12">
+        <v>437</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1417,15 +1591,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="44.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="35.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="33.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="27.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="16.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="33.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1438,89 +1615,151 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
-      <c r="D7" t="s">
-        <v>29</v>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8">
+        <v>446</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/data/customer_data.xlsx
+++ b/src/main/resources/data/customer_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9324" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
   <si>
     <t>customer_id</t>
   </si>
@@ -37,6 +37,9 @@
     <t>customer_name</t>
   </si>
   <si>
+    <t>province_city_area_code</t>
+  </si>
+  <si>
     <t>customer_type</t>
   </si>
   <si>
@@ -85,25 +88,40 @@
     <t>河北BIG大食袋食品公司</t>
   </si>
   <si>
+    <t>000023850efa49b380e70673b7bc8727</t>
+  </si>
+  <si>
+    <t>惠州市百星文化传媒有限公司</t>
+  </si>
+  <si>
     <t>d9f2860a636944b792d486f6623e4eed</t>
   </si>
   <si>
-    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE5</t>
-  </si>
-  <si>
-    <t>684BF6BD5829D2613460D115B0C8B4AD</t>
-  </si>
-  <si>
-    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE6</t>
-  </si>
-  <si>
-    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE7</t>
-  </si>
-  <si>
-    <t>8c9d06c140244485b64a837510f244e2</t>
-  </si>
-  <si>
-    <t>F34CF8F4C2BA4827A1550D5A0DF1CCE8</t>
+    <t>000032238f674641b9ab24cdd262f00e</t>
+  </si>
+  <si>
+    <t>和平县贝墩镇勇记农家特产店</t>
+  </si>
+  <si>
+    <t>0000362ba118412ba2e840940ae7d00f</t>
+  </si>
+  <si>
+    <t>中山市横栏镇华仔水产服务部</t>
+  </si>
+  <si>
+    <t>00004546b9bf46c69b9506432646ab4a</t>
+  </si>
+  <si>
+    <t>佛山市顺德区日勤物业管理有限公司</t>
+  </si>
+  <si>
+    <t>02181751c9e441ac8ddf474402bb334f</t>
+  </si>
+  <si>
+    <t>广东韶关国润再造烟叶有限公司</t>
+  </si>
+  <si>
+    <t>466A1C4FC4047E358848ED190D082F3F</t>
   </si>
   <si>
     <t>5BBDC0408063411D86F9A7BF3BD6DAB9</t>
@@ -112,18 +130,27 @@
     <t>河北君临药业有限公司</t>
   </si>
   <si>
+    <t>6S8MQBWX</t>
+  </si>
+  <si>
     <t>6E4906FF32E84BA2AEAA0C5E99D49A92</t>
   </si>
   <si>
     <t>河北倍智合成材料有限公司</t>
   </si>
   <si>
+    <t>8X5MPCWF</t>
+  </si>
+  <si>
     <t>DD330540FE724E0EA8FC0FABD370005E</t>
   </si>
   <si>
     <t>返利协议_客户_03</t>
   </si>
   <si>
+    <t>2NADB79W</t>
+  </si>
+  <si>
     <t>57266D99C9FB72AD09BFBFF4B8AC0218</t>
   </si>
   <si>
@@ -133,12 +160,18 @@
     <t>商务自动化测试代账客户_1761165296003</t>
   </si>
   <si>
+    <t>MRYQXXLN</t>
+  </si>
+  <si>
     <t>FDF34D4084D24180B386584E55780269</t>
   </si>
   <si>
     <t>河北永洋特钢集团有限公司</t>
   </si>
   <si>
+    <t>M8SRRWFN</t>
+  </si>
+  <si>
     <t>b763cad2fe2542018602d41fccc4ee39</t>
   </si>
   <si>
@@ -148,21 +181,12 @@
     <t>河北亿多宸建筑工程有限公司</t>
   </si>
   <si>
+    <t>6GYYAYTW</t>
+  </si>
+  <si>
     <t>DF910C299FBE1BDD4AC92093ECC77B2A</t>
   </si>
   <si>
-    <t>2DA38A922F3948D3AB3718608DC592E1</t>
-  </si>
-  <si>
-    <t>顺昂企业管理有限公司河北分公司</t>
-  </si>
-  <si>
-    <t>A8A6BFE023CF4316B3B3D1D2B79A93D7</t>
-  </si>
-  <si>
-    <t>河北博雅机械制造有限公司沧州分公司</t>
-  </si>
-  <si>
     <t>F12ADE025BFD428880B327BAA6A92993</t>
   </si>
   <si>
@@ -190,6 +214,63 @@
     <t>AP25PQDU</t>
   </si>
   <si>
+    <t>9B6D7B2D69EB4A54BF03A2E1A8F3F2B4</t>
+  </si>
+  <si>
+    <t>杭州市同源企业管理公司</t>
+  </si>
+  <si>
+    <t>4VD7CLAC</t>
+  </si>
+  <si>
+    <t>c4f1cfad504e49589169124f9dbdb36d</t>
+  </si>
+  <si>
+    <t>CE7F49D2F3F64EBE9332FBC22D01A465</t>
+  </si>
+  <si>
+    <t>上海市同源企业管理公司</t>
+  </si>
+  <si>
+    <t>K4QRKMLX</t>
+  </si>
+  <si>
+    <t>E10E887072B842DB83D1FEE7CBCBAE98</t>
+  </si>
+  <si>
+    <t>浙江喜唰唰企业服务有限公司宁波分公司</t>
+  </si>
+  <si>
+    <t>AJ5VWHJJ</t>
+  </si>
+  <si>
+    <t>FEC0BE4492CA4FC8A4DE54ED9FE4DD5C</t>
+  </si>
+  <si>
+    <t>杭州瑞邦财税管理公司</t>
+  </si>
+  <si>
+    <t>M6R28K2A</t>
+  </si>
+  <si>
+    <t>B0DA579B7D9D4913A2340E2D395B6B95</t>
+  </si>
+  <si>
+    <t>杭州喜乐多餐饮管理有限公司</t>
+  </si>
+  <si>
+    <t>NV8QZ7CN</t>
+  </si>
+  <si>
+    <t>9787848255C74D30B587809700045F44</t>
+  </si>
+  <si>
+    <t>德鸿瑞邦财税管理（杭州）有限公司</t>
+  </si>
+  <si>
+    <t>EUYC5JEX</t>
+  </si>
+  <si>
     <t>4E281275027F40868862718062B99CAA</t>
   </si>
   <si>
@@ -214,6 +295,9 @@
     <t>商务自动化测试代账客户_1761165214745</t>
   </si>
   <si>
+    <t>J4WX5HAA</t>
+  </si>
+  <si>
     <t>c28cf28dbbd24eb4b4132e11bbfe8697</t>
   </si>
   <si>
@@ -223,12 +307,18 @@
     <t>个代主联系人回测</t>
   </si>
   <si>
+    <t>RH3B2EQN</t>
+  </si>
+  <si>
     <t>2395C37CB3A04E42BAA3EE0BA3EB74A9</t>
   </si>
   <si>
     <t>ST202508141114test</t>
   </si>
   <si>
+    <t>4G4E49QU</t>
+  </si>
+  <si>
     <t>29F27552F248477B9B52C9BCDE62ECAC</t>
   </si>
   <si>
@@ -236,6 +326,15 @@
   </si>
   <si>
     <t>8M4R7GFW</t>
+  </si>
+  <si>
+    <t>3BC4CAB1A7EE4D2DAC088D5367CCAAB6</t>
+  </si>
+  <si>
+    <t>杭州小宋</t>
+  </si>
+  <si>
+    <t>CBXHMEDA</t>
   </si>
 </sst>
 </file>
@@ -851,9 +950,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
@@ -1167,22 +1269,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="33.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="14.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="15.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="21.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="36.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="36" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="21.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="36.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1197,139 +1300,186 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C2">
+        <v>130000</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>130000</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>130000</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="28.8" spans="1:7">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>130000</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>130000</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7">
-        <v>11111</v>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C7">
+        <v>440000</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>440000</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" t="s">
         <v>21</v>
       </c>
-      <c r="B8">
-        <v>11112</v>
-      </c>
-      <c r="C8">
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>440000</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9">
-        <v>11113</v>
-      </c>
-      <c r="C9">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
+        <v>440000</v>
+      </c>
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
-        <v>11114</v>
-      </c>
-      <c r="C10">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>440000</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>23</v>
+      <c r="G11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1342,18 +1492,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="35.1111111111111" customWidth="1"/>
     <col min="2" max="2" width="37.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="14.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="37.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="24.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="17.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="37.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1372,213 +1523,347 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2">
+        <v>130000</v>
+      </c>
+      <c r="D2">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>11</v>
-      </c>
-      <c r="E2">
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C3">
+        <v>130000</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>12</v>
-      </c>
-      <c r="E3">
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C4">
+        <v>130000</v>
+      </c>
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="D4">
-        <v>12</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4">
+        <v>446</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C5">
+        <v>130000</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5">
+        <v>446</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C6">
+        <v>130000</v>
+      </c>
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6">
+        <v>446</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C7">
+        <v>130000</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>446</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C8">
+        <v>130000</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="D8">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8">
+        <v>752</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C9">
+        <v>130000</v>
+      </c>
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="D9">
-        <v>18</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9">
+        <v>752</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C10">
+        <v>130000</v>
+      </c>
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10">
-        <v>752</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10">
+        <v>437</v>
+      </c>
+      <c r="G10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C11">
+        <v>330000</v>
+      </c>
+      <c r="D11">
         <v>2</v>
       </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11">
-        <v>752</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11">
+        <v>729</v>
+      </c>
+      <c r="G11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C12">
+        <v>310000</v>
+      </c>
+      <c r="D12">
         <v>2</v>
       </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12">
-        <v>437</v>
-      </c>
-      <c r="F12" t="s">
-        <v>39</v>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12">
+        <v>729</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <v>330200</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13">
+        <v>1048</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14">
+        <v>330000</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14">
+        <v>729</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15">
+        <v>330000</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15">
+        <v>1048</v>
+      </c>
+      <c r="G15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16">
+        <v>330000</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16">
+        <v>729</v>
+      </c>
+      <c r="G16" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1591,18 +1876,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="35.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="33.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="16.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
-    <col min="6" max="6" width="33.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="37.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="25.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="16.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="14.5555555555556" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="33.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1621,145 +1907,192 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C2">
+        <v>130000</v>
+      </c>
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>11</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C3">
+        <v>130000</v>
+      </c>
+      <c r="D3">
         <v>3</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C4">
+        <v>130000</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>12</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C5">
+        <v>130000</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5">
+        <v>1039</v>
+      </c>
+      <c r="G5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C6">
+        <v>130000</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="E6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6">
+        <v>1039</v>
+      </c>
+      <c r="G6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7">
+        <v>130000</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7">
+        <v>446</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8">
+        <v>130000</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8">
+        <v>446</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>330000</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9">
+        <v>1048</v>
+      </c>
+      <c r="G9" t="s">
         <v>64</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8">
-        <v>446</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/data/customer_data.xlsx
+++ b/src/main/resources/data/customer_data.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="128">
   <si>
     <t>customer_id</t>
   </si>
@@ -73,6 +73,24 @@
     <t>唐山星梦缘娱乐股份有限公司</t>
   </si>
   <si>
+    <t>609ac2e7678d4adcb3312b0125192069</t>
+  </si>
+  <si>
+    <t>承德市小六子商贸有限公司</t>
+  </si>
+  <si>
+    <t>99360ece3a7148708ddfaecaa028aec2</t>
+  </si>
+  <si>
+    <t>石家庄新干线公关策划有限公司</t>
+  </si>
+  <si>
+    <t>5A507D2A29D24C6EACD141B41B7D0C04</t>
+  </si>
+  <si>
+    <t>河北博雅机械制造有限公司保定分公司</t>
+  </si>
+  <si>
     <t>363924F1A2AD44E28831A615F70EE381</t>
   </si>
   <si>
@@ -113,6 +131,66 @@
   </si>
   <si>
     <t>佛山市顺德区日勤物业管理有限公司</t>
+  </si>
+  <si>
+    <t>0000563081c541208e56d4d8076f92b4</t>
+  </si>
+  <si>
+    <t>蔡燕辉</t>
+  </si>
+  <si>
+    <t>000057fe013441c1ad763243577df2ac</t>
+  </si>
+  <si>
+    <t>广州市戍华装饰工程有限公司第一分公司</t>
+  </si>
+  <si>
+    <t>00006040eefa4056b43fe40e70a02637</t>
+  </si>
+  <si>
+    <t>佛山市南海金孚特金属制品厂</t>
+  </si>
+  <si>
+    <t>000069b1f0de49bab57f4685de0d3f17</t>
+  </si>
+  <si>
+    <t>东莞纳齐电子有限公司</t>
+  </si>
+  <si>
+    <t>00006fd0e8214efb8f5258b0d7f032db</t>
+  </si>
+  <si>
+    <t>东莞市常平星泽五金加工店</t>
+  </si>
+  <si>
+    <t>000071748bdb4123853136ac34217238</t>
+  </si>
+  <si>
+    <t>佛山市顺德区溢顺钢铁贸易有限公司</t>
+  </si>
+  <si>
+    <t>000076a737e14c38bcda1a3568ee1d37</t>
+  </si>
+  <si>
+    <t>佛山市顺德区均安镇富景联塑料厂</t>
+  </si>
+  <si>
+    <t>00007c6a0f8e4a98b7330b7c3fd787bc</t>
+  </si>
+  <si>
+    <t>广东云数贸贸易有限公司</t>
+  </si>
+  <si>
+    <t>0000980f89cb419592b3982bda28ee49</t>
+  </si>
+  <si>
+    <t>廉江市横山金源木材加工厂</t>
+  </si>
+  <si>
+    <t>0000999c9d164467a80f2e140e20dac2</t>
+  </si>
+  <si>
+    <t>惠东县壹加壹农机专业合作社</t>
   </si>
   <si>
     <t>02181751c9e441ac8ddf474402bb334f</t>
@@ -1269,11 +1347,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="33.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.8888888888889" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.4444444444444" customWidth="1"/>
     <col min="4" max="4" width="14.5555555555556" customWidth="1"/>
     <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
@@ -1355,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1369,15 +1447,15 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6">
         <v>130000</v>
@@ -1391,67 +1469,61 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7">
+        <v>130000</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="28.8" spans="1:7">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="C7">
-        <v>440000</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" t="s">
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="C8">
+        <v>130000</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>440000</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C9">
-        <v>440000</v>
+        <v>130000</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C10">
         <v>440000</v>
@@ -1462,7 +1534,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1478,8 +1550,235 @@
       <c r="D11">
         <v>1</v>
       </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
       <c r="G11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
         <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>440000</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>440000</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14">
+        <v>440000</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15">
+        <v>440000</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16">
+        <v>440000</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17">
+        <v>440000</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18">
+        <v>440000</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19">
+        <v>440000</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>440000</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21">
+        <v>440000</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22">
+        <v>440000</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23">
+        <v>440000</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24">
+        <v>440000</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1529,10 +1828,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>130000</v>
@@ -1541,7 +1840,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1549,10 +1848,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>130000</v>
@@ -1561,7 +1860,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1569,10 +1868,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>130000</v>
@@ -1581,21 +1880,21 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F4">
         <v>446</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>130000</v>
@@ -1604,21 +1903,21 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>446</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>130000</v>
@@ -1627,21 +1926,21 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F6">
         <v>446</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <v>130000</v>
@@ -1650,21 +1949,21 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F7">
         <v>446</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>130000</v>
@@ -1673,21 +1972,21 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>752</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>130000</v>
@@ -1696,21 +1995,21 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F9">
         <v>752</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>130000</v>
@@ -1719,21 +2018,21 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="F10">
         <v>437</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C11">
         <v>330000</v>
@@ -1742,21 +2041,21 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="F11">
         <v>729</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C12">
         <v>310000</v>
@@ -1765,21 +2064,21 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="F12">
         <v>729</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C13">
         <v>330200</v>
@@ -1788,21 +2087,21 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F13">
         <v>1048</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C14">
         <v>330000</v>
@@ -1811,21 +2110,21 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F14">
         <v>729</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C15">
         <v>330000</v>
@@ -1834,21 +2133,21 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="F15">
         <v>1048</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C16">
         <v>330000</v>
@@ -1857,13 +2156,13 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="F16">
         <v>729</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1913,10 +2212,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C2">
         <v>130000</v>
@@ -1931,15 +2230,15 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>130000</v>
@@ -1954,15 +2253,15 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C4">
         <v>130000</v>
@@ -1977,15 +2276,15 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C5">
         <v>130000</v>
@@ -1994,21 +2293,21 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="F5">
         <v>1039</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C6">
         <v>130000</v>
@@ -2017,21 +2316,21 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="F6">
         <v>1039</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <v>130000</v>
@@ -2040,21 +2339,21 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="F7">
         <v>446</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C8">
         <v>130000</v>
@@ -2063,21 +2362,21 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="F8">
         <v>446</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C9">
         <v>330000</v>
@@ -2086,13 +2385,13 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="F9">
         <v>1048</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
